--- a/artfynd/A 18259-2026 artfynd.xlsx
+++ b/artfynd/A 18259-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>14189333</v>
       </c>
       <c r="B2" t="n">
-        <v>39445</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506825.1746061285</v>
+        <v>506825</v>
       </c>
       <c r="R2" t="n">
-        <v>6531669.580384248</v>
+        <v>6531670</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,19 +762,9 @@
           <t>2009-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 18259-2026 artfynd.xlsx
+++ b/artfynd/A 18259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,8 +808,16 @@
           <t>Privat inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14189333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18259-2026 artfynd.xlsx
+++ b/artfynd/A 18259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14189333</v>
+        <v>135531683</v>
       </c>
       <c r="B2" t="n">
-        <v>40128</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102471</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerväddsantennmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nemophora metallica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Poda, 1761)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gålsjö 3850/0450, Nrk</t>
+          <t>djupsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506825</v>
+        <v>506552</v>
       </c>
       <c r="R2" t="n">
-        <v>6531670</v>
+        <v>6531743</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,17 +753,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-06-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-06-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På Knautia</t>
+          <t>Kåda hela tallen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,29 +785,280 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531683</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135531568</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>djupsjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506812</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6531589</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack Gammal stor tall Märkt no 19 av Skogsförvaltaren</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531568</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14189333</v>
+      </c>
+      <c r="B4" t="n">
+        <v>40128</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102471</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Åkerväddsantennmal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nemophora metallica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Poda, 1761)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gålsjö 3850/0450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506825</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6531670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-06-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Privat inventering</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/14189333</t>
         </is>
@@ -817,6 +1067,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18259-2026 artfynd.xlsx
+++ b/artfynd/A 18259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135531683</v>
+        <v>135531568</v>
       </c>
       <c r="B2" t="n">
         <v>57980</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506552</v>
+        <v>506812</v>
       </c>
       <c r="R2" t="n">
-        <v>6531743</v>
+        <v>6531589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kåda hela tallen</t>
+          <t>Färska ringhack Gammal stor tall Märkt no 19 av Skogsförvaltaren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,16 +799,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135531683</t>
+          <t>https://artportalen.se/Sighting/135531568</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135531568</v>
+        <v>14189333</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>40128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,45 +816,56 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102471</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Åkerväddsantennmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nemophora metallica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(Poda, 1761)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>djupsjön, Nrk</t>
+          <t>Gålsjö 3850/0450, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506812</v>
+        <v>506825</v>
       </c>
       <c r="R3" t="n">
-        <v>6531589</v>
+        <v>6531670</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +889,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2009-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2009-06-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack Gammal stor tall Märkt no 19 av Skogsförvaltaren</t>
+          <t>På Knautia</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,155 +911,29 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Privat inventering</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135531568</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>14189333</v>
-      </c>
-      <c r="B4" t="n">
-        <v>40128</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>102471</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Åkerväddsantennmal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Nemophora metallica</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Poda, 1761)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Gålsjö 3850/0450, Nrk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>506825</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6531670</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2009-06-29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2009-06-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Knautia</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägren</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Privat inventering</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/14189333</t>
         </is>
@@ -1068,7 +943,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18259-2026 artfynd.xlsx
+++ b/artfynd/A 18259-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135531568</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
